--- a/esyluban/examples/release/DataTables/test/test_null_datas/test_null.xlsx
+++ b/esyluban/examples/release/DataTables/test/test_null_datas/test_null.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="13.125" customWidth="1" style="4" min="5" max="5"/>
@@ -512,8 +512,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6">
       <c r="B6" s="0" t="n">
         <v>1</v>
@@ -670,20 +668,10 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
